--- a/SiPM_Sensor_Array/Outjob-Outputs/BOM/SiPM_Array-v1-BOM.xlsx
+++ b/SiPM_Sensor_Array/Outjob-Outputs/BOM/SiPM_Array-v1-BOM.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\ffff\RAD-V3-PCB\SiPM_Sensor_Array\Outjob-Outputs\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\RAD-V3-PCB\SiPM_Sensor_Array\Outjob-Outputs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC1A0897-4090-4272-8511-57E26E83BB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49F00267-323A-4C6C-8054-1DAAF375B5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{399FF05A-1FA6-4FDD-8873-D879FBE1FBB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8143E680-549F-46F0-B77E-A70799F379B4}"/>
   </bookViews>
   <sheets>
-    <sheet name="SiPM_Array-v1-BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'SiPM_Array-v1-BOM'!$1:$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,120 +31,156 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+  <si>
+    <t>PCB Name:</t>
+  </si>
+  <si>
+    <t>Bill of Materials (BOM) for Assembly</t>
+  </si>
+  <si>
+    <t>Project:</t>
+  </si>
+  <si>
+    <t>PCB Revision:</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>Time:</t>
+  </si>
+  <si>
+    <t>PCB Designer:</t>
+  </si>
+  <si>
+    <t>&lt;Parameter Project not found&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Parameter DesignName not found&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Parameter BoardRevision not found&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Parameter Designer not found&gt;</t>
+  </si>
+  <si>
+    <t>13/09/2026</t>
+  </si>
+  <si>
+    <t>10:16 pm</t>
+  </si>
   <si>
     <t>Designator</t>
   </si>
   <si>
+    <t>3V3, GND, SCL, SDA, VAN1, VAN2, VBR</t>
+  </si>
+  <si>
+    <t>B1, B2</t>
+  </si>
+  <si>
+    <t>C1, C2, C3</t>
+  </si>
+  <si>
+    <t>J1, J2</t>
+  </si>
+  <si>
+    <t>R1, R2</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Comment</t>
+    <t>TEST POINT (BLUE) - MINIATURE</t>
+  </si>
+  <si>
+    <t>The S14160 series achieve higher PDE (photon detection efficiency) and lower operation voltage than other MPPC to adapt for PET and radiation monitor application.-Higher PDE: 50% at p, Vop=VBR + 2.7 V</t>
+  </si>
+  <si>
+    <t>Passive - Capacitor, 0805, 100uF Max, X5R, 6.3V ±20%, -55°C ~ 85°C, 0805 (2012 Metric). 20uF @ 6.3V</t>
+  </si>
+  <si>
+    <t>Res 0805 2k 1% 125mW</t>
+  </si>
+  <si>
+    <t>No Description Available</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>5267</t>
+  </si>
+  <si>
+    <t>S14160-3050HS</t>
+  </si>
+  <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>DF17(3.0)-20DS-0.5V(57)</t>
+  </si>
+  <si>
+    <t>CR0805-FX-2001ELF</t>
+  </si>
+  <si>
+    <t>TMP112AQDRLRQ1</t>
   </si>
   <si>
     <t>MF Part No.</t>
   </si>
   <si>
+    <t>GRM21BR60J107ME15L</t>
+  </si>
+  <si>
+    <t>Package</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
+    <t>0805 Bourns</t>
+  </si>
+  <si>
+    <t>Supplier 1</t>
+  </si>
+  <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>Supplier 1 Part No.</t>
+  </si>
+  <si>
+    <t>490-GRM155R61E225KE11JCT-ND</t>
+  </si>
+  <si>
+    <t>APSS Standard Part</t>
+  </si>
+  <si>
+    <t>APSS Standard</t>
+  </si>
+  <si>
     <t>Quantity</t>
-  </si>
-  <si>
-    <t>Supplier 1</t>
-  </si>
-  <si>
-    <t>Supplier 1 Part No.</t>
-  </si>
-  <si>
-    <t>Package</t>
-  </si>
-  <si>
-    <t>APSS Standard Part</t>
-  </si>
-  <si>
-    <t>3V3, GND, SCL, SDA, VAN1, VAN2, VBR</t>
-  </si>
-  <si>
-    <t>TEST POINT (BLUE) - MINIATURE</t>
-  </si>
-  <si>
-    <t>5267</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>B1, B2</t>
-  </si>
-  <si>
-    <t>The S14160 series achieve higher PDE (photon detection efficiency) and lower operation voltage than other MPPC to adapt for PET and radiation monitor application.-Higher PDE: 50% at p, Vop=VBR + 2.7 V</t>
-  </si>
-  <si>
-    <t>S14160-3050HS</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Passive - Capacitor, 0805, 100uF Max, X5R, 6.3V ±20%, -55°C ~ 85°C, 0805 (2012 Metric). 20uF @ 6.3V</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>GRM21BR60J107ME15L</t>
-  </si>
-  <si>
-    <t>Digikey</t>
-  </si>
-  <si>
-    <t>490-GRM155R61E225KE11JCT-ND</t>
-  </si>
-  <si>
-    <t>0805</t>
-  </si>
-  <si>
-    <t>APSS Standard</t>
-  </si>
-  <si>
-    <t>J2, J3</t>
-  </si>
-  <si>
-    <t>DF17(3.0)-20DS-0.5V(57)</t>
-  </si>
-  <si>
-    <t>R1, R2</t>
-  </si>
-  <si>
-    <t>Res 0805 2k 1% 125mW | Bourns CR0805-FX-2001ELF</t>
-  </si>
-  <si>
-    <t>CR0805-FX-2001ELF</t>
-  </si>
-  <si>
-    <t>0805 Bourns</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>No Description Available</t>
-  </si>
-  <si>
-    <t>TMP112AQDRLRQ1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,8 +188,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,12 +230,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD3D3D3"/>
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -193,16 +270,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -218,6 +340,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>498751</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>180147</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2877378</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>145380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD2732D5-888C-41E1-9B0A-2336FDB160A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1111664" y="362364"/>
+          <a:ext cx="4159388" cy="1127974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -536,180 +707,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3548453-1011-4FE2-BC55-9DE8557B6D91}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B358C88E-7CF8-41D0-B20D-DBF0AE37A859}">
+  <dimension ref="B2:J16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.25" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
-    <col min="7" max="7" width="24.75" customWidth="1"/>
-    <col min="8" max="8" width="16.125" customWidth="1"/>
-    <col min="9" max="9" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="50.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="38.42578125" customWidth="1"/>
+    <col min="9" max="9" width="22.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="4" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="2" spans="2:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:C8"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>